--- a/backtest_runs/20260410_193731/by_symbol/RCML/RCML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/RCML/RCML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-8085.720000000008</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>91914.28</v>
@@ -725,7 +725,7 @@
         <v>-2.579999999997654</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>101042.32</v>
@@ -909,7 +909,7 @@
         <v>-7892.220000000008</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>94772.91999999998</v>
@@ -1139,7 +1139,7 @@
         <v>-5.159999999995307</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>95879.73999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-4920.059999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>90959.67999999999</v>
